--- a/data/trans_dic/P43-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P43-Provincia-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -518,22 +518,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado alguna vez una mamografía por prescripción de algún especialista</t>
+          <t>Población a la que le han realizado alguna vez una mamografía por prescripción de algún especialista (tasa de respuesta: 99,33%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,20 +537,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -595,26 +583,6 @@
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -631,10 +599,6 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -649,22 +613,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,26 +647,6 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>62,34%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>34,78%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>51,64%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>50,45%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>62,34%</t>
         </is>
@@ -717,62 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>28,61; 40,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>45,56; 57,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>44,06; 56,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>55,21; 68,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,53; 41,47</t>
+          <t>28,61; 40,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,34; 58,0</t>
+          <t>45,56; 57,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,55; 56,7</t>
+          <t>44,06; 56,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>55,12; 68,85</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>28,53; 41,47</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>45,34; 58,0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>44,55; 56,7</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>55,12; 68,85</t>
+          <t>55,21; 68,38</t>
         </is>
       </c>
     </row>
@@ -789,22 +713,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,26 +747,6 @@
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>54,76%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>36,41%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>41,77%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>51,04%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>54,76%</t>
         </is>
@@ -857,62 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>32,55; 40,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37,37; 46,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>46,81; 55,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>49,98; 58,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,08; 40,61</t>
+          <t>32,55; 40,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,02; 46,28</t>
+          <t>37,37; 46,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,27; 55,48</t>
+          <t>46,81; 55,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>50,15; 59,19</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>32,08; 40,61</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>37,02; 46,28</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>46,27; 55,48</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>50,15; 59,19</t>
+          <t>49,98; 58,92</t>
         </is>
       </c>
     </row>
@@ -929,22 +813,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,26 +847,6 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>53,83%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>40,77%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>46,75%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>56,69%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>53,83%</t>
         </is>
@@ -997,62 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>35,16; 46,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>41,38; 53,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>51,41; 62,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>48,7; 59,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,57; 46,23</t>
+          <t>35,16; 46,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,26; 52,31</t>
+          <t>41,38; 53,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,2; 62,14</t>
+          <t>51,41; 62,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48,18; 59,14</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>35,57; 46,23</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>41,26; 52,31</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>51,2; 62,14</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>48,18; 59,14</t>
+          <t>48,7; 59,01</t>
         </is>
       </c>
     </row>
@@ -1069,22 +913,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,26 +947,6 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>47,21%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>41,22%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>48,37%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>52,84%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>47,21%</t>
         </is>
@@ -1137,62 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>36,04; 45,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>43,25; 53,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>47,0; 58,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>26,67; 61,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>36,52; 46,35</t>
+          <t>36,04; 45,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,26; 53,42</t>
+          <t>43,25; 53,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,89; 57,7</t>
+          <t>47,0; 58,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,33; 62,12</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>36,52; 46,35</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>43,26; 53,42</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>47,89; 57,7</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>25,33; 62,12</t>
+          <t>26,67; 61,69</t>
         </is>
       </c>
     </row>
@@ -1209,22 +1013,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,26 +1047,6 @@
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>72,84%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>29,92%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>47,76%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>52,68%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>72,84%</t>
         </is>
@@ -1277,62 +1061,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>23,71; 36,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>41,03; 54,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>46,32; 59,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>66,77; 77,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,68; 37,1</t>
+          <t>23,71; 36,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,27; 54,64</t>
+          <t>41,03; 54,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,01; 59,09</t>
+          <t>46,32; 59,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>66,35; 77,67</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>23,68; 37,1</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>41,27; 54,64</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>46,01; 59,09</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>66,35; 77,67</t>
+          <t>66,77; 77,66</t>
         </is>
       </c>
     </row>
@@ -1349,22 +1113,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,26 +1147,6 @@
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>53,26%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>38,28%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>48,62%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>49,96%</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>53,26%</t>
         </is>
@@ -1417,62 +1161,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>33,12; 44,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>42,37; 54,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>44,13; 56,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>47,43; 58,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32,83; 44,63</t>
+          <t>33,12; 44,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>42,81; 54,81</t>
+          <t>42,37; 54,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,03; 56,0</t>
+          <t>44,13; 56,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>47,86; 59,0</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>32,83; 44,63</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>42,81; 54,81</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>44,03; 56,0</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>47,86; 59,0</t>
+          <t>47,43; 58,69</t>
         </is>
       </c>
     </row>
@@ -1489,22 +1213,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,26 +1247,6 @@
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>73,63%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>43,66%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>51,07%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>42,34%</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>73,63%</t>
         </is>
@@ -1557,62 +1261,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>39,69; 47,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>47,35; 55,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>39,06; 46,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>60,76; 88,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>39,78; 47,77</t>
+          <t>39,69; 47,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,46; 55,12</t>
+          <t>47,35; 55,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,43; 46,01</t>
+          <t>39,06; 46,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>60,11; 88,31</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>39,78; 47,77</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>47,46; 55,12</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>38,43; 46,01</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>60,11; 88,31</t>
+          <t>60,76; 88,35</t>
         </is>
       </c>
     </row>
@@ -1629,22 +1313,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,26 +1347,6 @@
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>37,71%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>34,37%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>44,61%</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>50,49%</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>37,71%</t>
         </is>
@@ -1697,62 +1361,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>30,81; 37,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>41,35; 48,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>46,75; 53,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>34,2; 40,72</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>31,32; 37,96</t>
+          <t>30,81; 37,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,93; 48,19</t>
+          <t>41,35; 48,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,88; 53,9</t>
+          <t>46,75; 53,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>34,36; 41,76</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>31,32; 37,96</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>40,93; 48,19</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>46,88; 53,9</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>34,36; 41,76</t>
+          <t>34,2; 40,72</t>
         </is>
       </c>
     </row>
@@ -1769,22 +1413,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1803,26 +1447,6 @@
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>55,92%</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>37,91%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>47,14%</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>49,93%</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>55,92%</t>
         </is>
@@ -1837,62 +1461,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>36,25; 39,49</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>45,45; 48,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>48,25; 51,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>51,07; 66,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>36,19; 39,57</t>
+          <t>36,25; 39,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>45,44; 48,92</t>
+          <t>45,45; 48,86</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>48,16; 51,62</t>
+          <t>48,25; 51,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>51,38; 66,52</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>36,19; 39,57</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>45,44; 48,92</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>48,16; 51,62</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>51,38; 66,52</t>
+          <t>51,07; 66,18</t>
         </is>
       </c>
     </row>
@@ -1904,17 +1508,16 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A10:A11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A14:A15"/>
@@ -1929,7 +1532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1942,22 +1545,18 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado alguna vez una mamografía por prescripción de algún especialista</t>
+          <t>Población a la que le han realizado alguna vez una mamografía por prescripción de algún especialista (tasa de respuesta: 99,33%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,20 +1564,12 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -2019,26 +1610,6 @@
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -2055,10 +1626,6 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -2073,22 +1640,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>129</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2107,26 +1674,6 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>236</t>
         </is>
@@ -2141,22 +1688,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>90728</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>145577</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>144413</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>116092</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2175,26 +1722,6 @@
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>116092</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>90728</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>145577</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>144413</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>116092</t>
         </is>
@@ -2209,62 +1736,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>74626; 106701</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>128434; 162817</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>126115; 160812</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>102801; 127329</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>74420; 108178</t>
+          <t>74626; 106701</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>127803; 163503</t>
+          <t>128434; 162817</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>127523; 162321</t>
+          <t>126115; 160812</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>102639; 128207</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>74420; 108178</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>127803; 163503</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>127523; 162321</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>102639; 128207</t>
+          <t>102801; 127329</t>
         </is>
       </c>
     </row>
@@ -2281,22 +1788,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>179</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>195</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>238</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>336</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2315,26 +1822,6 @@
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
@@ -2349,22 +1836,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>182098</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>218325</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>266175</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>222489</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2383,26 +1870,6 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>222489</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>182098</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>218325</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>266175</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>222489</t>
         </is>
@@ -2417,62 +1884,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>162781; 203512</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>195339; 243894</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>244101; 290309</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>203073; 239428</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>160445; 203124</t>
+          <t>162781; 203512</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>193526; 241922</t>
+          <t>195339; 243894</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>241290; 289312</t>
+          <t>244101; 290309</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>203788; 240511</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>160445; 203124</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>193526; 241922</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>241290; 289312</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>203788; 240511</t>
+          <t>203073; 239428</t>
         </is>
       </c>
     </row>
@@ -2489,22 +1936,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>137</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>144</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2523,26 +1970,6 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>241</t>
         </is>
@@ -2557,22 +1984,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>135996</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>158977</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>187999</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>135628</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2591,26 +2018,6 @@
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>135628</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>135996</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>158977</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>187999</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>135628</t>
         </is>
@@ -2625,62 +2032,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>117273; 153699</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>140698; 180355</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>170485; 205875</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>122705; 148684</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>118642; 154203</t>
+          <t>117273; 153699</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>140283; 177865</t>
+          <t>140698; 180355</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>169797; 206070</t>
+          <t>170485; 205875</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>121397; 149008</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>118642; 154203</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>140283; 177865</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>169797; 206070</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>121397; 149008</t>
+          <t>122705; 148684</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2084,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>161</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>303</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2731,26 +2118,6 @@
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>303</t>
         </is>
@@ -2765,22 +2132,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>153130</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>187193</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>203988</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>182240</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2799,26 +2166,6 @@
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>182240</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>153130</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>187193</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>203988</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>182240</t>
         </is>
@@ -2833,62 +2180,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>133868; 170833</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>167376; 207632</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>181471; 224547</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>102968; 238161</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>135664; 172169</t>
+          <t>133868; 170833</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>167399; 206724</t>
+          <t>167376; 207632</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>184874; 222759</t>
+          <t>181471; 224547</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>97780; 239819</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>135664; 172169</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>167399; 206724</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>184874; 222759</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>97780; 239819</t>
+          <t>102968; 238161</t>
         </is>
       </c>
     </row>
@@ -2905,22 +2232,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>293</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2939,26 +2266,6 @@
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>293</t>
         </is>
@@ -2973,22 +2280,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>61380</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>104880</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>114692</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>111978</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3007,26 +2314,6 @@
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>111978</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>61380</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>104880</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>114692</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>111978</t>
         </is>
@@ -3041,62 +2328,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>48634; 75344</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>90099; 119698</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>100838; 128818</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>102638; 119390</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>48577; 76104</t>
+          <t>48634; 75344</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>90617; 119988</t>
+          <t>90099; 119698</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>100164; 128648</t>
+          <t>100838; 128818</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>102000; 119394</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>48577; 76104</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>90617; 119988</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>100164; 128648</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>102000; 119394</t>
+          <t>102638; 119390</t>
         </is>
       </c>
     </row>
@@ -3113,22 +2380,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>103</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>131</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>128</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -3147,26 +2414,6 @@
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>241</t>
         </is>
@@ -3181,22 +2428,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>106102</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>136147</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>136442</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>111753</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3215,26 +2462,6 @@
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>111753</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>106102</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>136147</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>136442</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>111753</t>
         </is>
@@ -3249,62 +2476,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>91798; 123598</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>118661; 153174</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>120525; 153488</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>99523; 123142</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>91019; 123718</t>
+          <t>91798; 123598</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>119871; 153498</t>
+          <t>118661; 153174</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>120243; 152943</t>
+          <t>120525; 153488</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>100424; 123793</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>91019; 123718</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>119871; 153498</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>120243; 152943</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>100424; 123793</t>
+          <t>99523; 123142</t>
         </is>
       </c>
     </row>
@@ -3321,22 +2528,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>315</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>257</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3355,26 +2562,6 @@
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>450</t>
         </is>
@@ -3389,22 +2576,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>276948</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>352823</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>288524</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>484922</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3423,26 +2610,6 @@
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>484922</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>276948</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>352823</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>288524</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>484922</t>
         </is>
@@ -3457,62 +2624,42 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>251764; 302755</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>327108; 381563</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>266166; 313675</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>400214; 581905</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>252323; 302973</t>
+          <t>251764; 302755</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>327874; 380807</t>
+          <t>327108; 381563</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>261832; 313530</t>
+          <t>266166; 313675</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>395900; 581663</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>252323; 302973</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>327874; 380807</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>261832; 313530</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>395900; 581663</t>
+          <t>400214; 581905</t>
         </is>
       </c>
     </row>
@@ -3529,22 +2676,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>255</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>327</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>361</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>367</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3563,26 +2710,6 @@
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>367</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>367</t>
         </is>
@@ -3597,22 +2724,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>267060</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>363327</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>415068</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>218035</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3631,26 +2758,6 @@
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>218035</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>267060</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>363327</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>415068</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>218035</t>
         </is>
@@ -3665,62 +2772,42 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>239385; 294297</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>336745; 395371</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>384295; 443503</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>197773; 235425</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>243315; 294952</t>
+          <t>239385; 294297</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>333362; 392492</t>
+          <t>336745; 395371</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>385394; 443133</t>
+          <t>384295; 443503</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>198655; 241454</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>243315; 294952</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>333362; 392492</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>385394; 443133</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>198655; 241454</t>
+          <t>197773; 235425</t>
         </is>
       </c>
     </row>
@@ -3737,22 +2824,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1523</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3771,26 +2858,6 @@
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>2467</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>1252</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>1595</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>2467</t>
         </is>
@@ -3805,22 +2872,22 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1273441</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1667249</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1757300</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1583137</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3839,26 +2906,6 @@
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1583137</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>1273441</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>1667249</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>1757300</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>1583137</t>
         </is>
@@ -3873,62 +2920,42 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1217806; 1326804</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1607282; 1727835</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1698387; 1824187</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1445705; 1873457</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1215683; 1329323</t>
+          <t>1217806; 1326804</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1606844; 1729955</t>
+          <t>1607282; 1727835</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1694936; 1816789</t>
+          <t>1698387; 1824187</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1454515; 1883137</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>1215683; 1329323</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>1606844; 1729955</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>1694936; 1816789</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>1454515; 1883137</t>
+          <t>1445705; 1873457</t>
         </is>
       </c>
     </row>
@@ -3940,7 +2967,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
@@ -3948,10 +2975,9 @@
     <mergeCell ref="A25:A27"/>
     <mergeCell ref="A28:A30"/>
     <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A1:B2"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>

--- a/data/trans_dic/P43-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P43-Provincia-trans_dic.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>58,28%</t>
         </is>
       </c>
     </row>
@@ -661,42 +661,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28,61; 40,91</t>
+          <t>29,45; 40,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>45,56; 57,76</t>
+          <t>45,79; 57,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44,06; 56,18</t>
+          <t>44,87; 56,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55,21; 68,38</t>
+          <t>52,21; 63,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,61; 40,91</t>
+          <t>29,45; 40,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,56; 57,76</t>
+          <t>45,79; 57,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,06; 56,18</t>
+          <t>44,87; 56,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>55,21; 68,38</t>
+          <t>52,21; 63,69</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>53,58%</t>
         </is>
       </c>
     </row>
@@ -761,42 +761,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,55; 40,69</t>
+          <t>32,14; 40,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,37; 46,66</t>
+          <t>37,11; 46,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46,81; 55,67</t>
+          <t>46,62; 54,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49,98; 58,92</t>
+          <t>48,98; 58,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,55; 40,69</t>
+          <t>32,14; 40,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,37; 46,66</t>
+          <t>37,11; 46,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,81; 55,67</t>
+          <t>46,62; 54,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>49,98; 58,92</t>
+          <t>48,98; 58,25</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,8%</t>
         </is>
       </c>
     </row>
@@ -861,42 +861,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35,16; 46,08</t>
+          <t>35,97; 45,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>41,38; 53,04</t>
+          <t>41,03; 52,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51,41; 62,08</t>
+          <t>51,01; 61,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48,7; 59,01</t>
+          <t>48,0; 59,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,16; 46,08</t>
+          <t>35,97; 45,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,38; 53,04</t>
+          <t>41,03; 52,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,41; 62,08</t>
+          <t>51,01; 61,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48,7; 59,01</t>
+          <t>48,0; 59,26</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>51,88%</t>
         </is>
       </c>
     </row>
@@ -961,42 +961,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,04; 45,99</t>
+          <t>36,41; 46,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43,25; 53,65</t>
+          <t>43,19; 53,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,0; 58,16</t>
+          <t>47,39; 57,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,67; 61,69</t>
+          <t>46,34; 57,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>36,04; 45,99</t>
+          <t>36,41; 46,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,25; 53,65</t>
+          <t>43,19; 53,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,0; 58,16</t>
+          <t>47,39; 57,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26,67; 61,69</t>
+          <t>46,34; 57,87</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>71,29%</t>
         </is>
       </c>
     </row>
@@ -1061,42 +1061,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>23,71; 36,73</t>
+          <t>23,54; 36,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41,03; 54,51</t>
+          <t>41,0; 54,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46,32; 59,17</t>
+          <t>46,61; 59,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66,77; 77,66</t>
+          <t>65,43; 76,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,71; 36,73</t>
+          <t>23,54; 36,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,03; 54,51</t>
+          <t>41,0; 54,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,32; 59,17</t>
+          <t>46,61; 59,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>66,77; 77,66</t>
+          <t>65,43; 76,79</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,53%</t>
         </is>
       </c>
     </row>
@@ -1161,42 +1161,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33,12; 44,59</t>
+          <t>32,94; 44,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>42,37; 54,7</t>
+          <t>42,3; 54,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>44,13; 56,2</t>
+          <t>43,47; 55,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47,43; 58,69</t>
+          <t>48,25; 59,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,12; 44,59</t>
+          <t>32,94; 44,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>42,37; 54,7</t>
+          <t>42,3; 54,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,13; 56,2</t>
+          <t>43,47; 55,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>47,43; 58,69</t>
+          <t>48,25; 59,13</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>61,11%</t>
         </is>
       </c>
     </row>
@@ -1261,42 +1261,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>39,69; 47,73</t>
+          <t>39,58; 47,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>47,35; 55,23</t>
+          <t>47,0; 55,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39,06; 46,03</t>
+          <t>38,3; 46,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60,76; 88,35</t>
+          <t>56,9; 65,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>39,69; 47,73</t>
+          <t>39,58; 47,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,35; 55,23</t>
+          <t>47,0; 55,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,06; 46,03</t>
+          <t>38,3; 46,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>60,76; 88,35</t>
+          <t>56,9; 65,0</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,16%</t>
         </is>
       </c>
     </row>
@@ -1361,42 +1361,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>30,81; 37,88</t>
+          <t>31,18; 37,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>41,35; 48,54</t>
+          <t>41,02; 48,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46,75; 53,95</t>
+          <t>46,91; 54,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34,2; 40,72</t>
+          <t>34,21; 40,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>30,81; 37,88</t>
+          <t>31,18; 37,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,35; 48,54</t>
+          <t>41,02; 48,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,75; 53,95</t>
+          <t>46,91; 54,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>34,2; 40,72</t>
+          <t>34,21; 40,61</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>52,32%</t>
         </is>
       </c>
     </row>
@@ -1461,42 +1461,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>36,25; 39,49</t>
+          <t>36,16; 39,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>45,45; 48,86</t>
+          <t>45,56; 48,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>48,25; 51,83</t>
+          <t>48,24; 51,71</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>51,07; 66,18</t>
+          <t>50,59; 53,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>36,25; 39,49</t>
+          <t>36,16; 39,59</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>45,45; 48,86</t>
+          <t>45,56; 48,86</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>48,25; 51,83</t>
+          <t>48,24; 51,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>51,07; 66,18</t>
+          <t>50,59; 53,89</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>116092</t>
+          <t>118755</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>116092</t>
+          <t>118755</t>
         </is>
       </c>
     </row>
@@ -1736,42 +1736,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>74626; 106701</t>
+          <t>76826; 106591</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>128434; 162817</t>
+          <t>129089; 162659</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>126115; 160812</t>
+          <t>128457; 162630</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>102801; 127329</t>
+          <t>106382; 129764</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>74626; 106701</t>
+          <t>76826; 106591</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>128434; 162817</t>
+          <t>129089; 162659</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>126115; 160812</t>
+          <t>128457; 162630</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>102801; 127329</t>
+          <t>106382; 129764</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>222489</t>
+          <t>230743</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>222489</t>
+          <t>230743</t>
         </is>
       </c>
     </row>
@@ -1884,42 +1884,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>162781; 203512</t>
+          <t>160732; 203427</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>195339; 243894</t>
+          <t>193969; 241108</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>244101; 290309</t>
+          <t>243087; 286539</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>203073; 239428</t>
+          <t>210906; 250821</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>162781; 203512</t>
+          <t>160732; 203427</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>195339; 243894</t>
+          <t>193969; 241108</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>244101; 290309</t>
+          <t>243087; 286539</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>203073; 239428</t>
+          <t>210906; 250821</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>135628</t>
+          <t>137858</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>135628</t>
+          <t>137858</t>
         </is>
       </c>
     </row>
@@ -2032,42 +2032,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>117273; 153699</t>
+          <t>119976; 153399</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>140698; 180355</t>
+          <t>139500; 178110</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>170485; 205875</t>
+          <t>169138; 205375</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>122705; 148684</t>
+          <t>122995; 151838</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>117273; 153699</t>
+          <t>119976; 153399</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>140698; 180355</t>
+          <t>139500; 178110</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>170485; 205875</t>
+          <t>169138; 205375</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>122705; 148684</t>
+          <t>122995; 151838</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>182240</t>
+          <t>166721</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>182240</t>
+          <t>166721</t>
         </is>
       </c>
     </row>
@@ -2180,42 +2180,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>133868; 170833</t>
+          <t>135238; 171700</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>167376; 207632</t>
+          <t>167124; 207329</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>181471; 224547</t>
+          <t>182957; 223623</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>102968; 238161</t>
+          <t>148907; 185965</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>133868; 170833</t>
+          <t>135238; 171700</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>167376; 207632</t>
+          <t>167124; 207329</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>181471; 224547</t>
+          <t>182957; 223623</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>102968; 238161</t>
+          <t>148907; 185965</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>111978</t>
+          <t>119840</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>111978</t>
+          <t>119840</t>
         </is>
       </c>
     </row>
@@ -2328,42 +2328,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>48634; 75344</t>
+          <t>48286; 74351</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>90099; 119698</t>
+          <t>90031; 119306</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>100838; 128818</t>
+          <t>101488; 128626</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>102638; 119390</t>
+          <t>109998; 129087</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>48634; 75344</t>
+          <t>48286; 74351</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>90099; 119698</t>
+          <t>90031; 119306</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>100838; 128818</t>
+          <t>101488; 128626</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>102638; 119390</t>
+          <t>109998; 129087</t>
         </is>
       </c>
     </row>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>111753</t>
+          <t>115329</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>111753</t>
+          <t>115329</t>
         </is>
       </c>
     </row>
@@ -2476,42 +2476,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>91798; 123598</t>
+          <t>91309; 122832</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>118661; 153174</t>
+          <t>118457; 152846</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>120525; 153488</t>
+          <t>118728; 151484</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>99523; 123142</t>
+          <t>103940; 127394</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>91798; 123598</t>
+          <t>91309; 122832</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>118661; 153174</t>
+          <t>118457; 152846</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>120525; 153488</t>
+          <t>118728; 151484</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>99523; 123142</t>
+          <t>103940; 127394</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>484922</t>
+          <t>328020</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>484922</t>
+          <t>328020</t>
         </is>
       </c>
     </row>
@@ -2624,42 +2624,42 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>251764; 302755</t>
+          <t>251065; 301695</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>327108; 381563</t>
+          <t>324685; 382315</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>266166; 313675</t>
+          <t>260971; 316616</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>400214; 581905</t>
+          <t>305427; 348865</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>251764; 302755</t>
+          <t>251065; 301695</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>327108; 381563</t>
+          <t>324685; 382315</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>266166; 313675</t>
+          <t>260971; 316616</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>400214; 581905</t>
+          <t>305427; 348865</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>218035</t>
+          <t>249226</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>218035</t>
+          <t>249226</t>
         </is>
       </c>
     </row>
@@ -2772,42 +2772,42 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>239385; 294297</t>
+          <t>242245; 291791</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>336745; 395371</t>
+          <t>334089; 392871</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>384295; 443503</t>
+          <t>385665; 444311</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>197773; 235425</t>
+          <t>229425; 272368</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>239385; 294297</t>
+          <t>242245; 291791</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>336745; 395371</t>
+          <t>334089; 392871</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>384295; 443503</t>
+          <t>385665; 444311</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>197773; 235425</t>
+          <t>229425; 272368</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1583137</t>
+          <t>1466492</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1583137</t>
+          <t>1466492</t>
         </is>
       </c>
     </row>
@@ -2920,42 +2920,42 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1217806; 1326804</t>
+          <t>1214792; 1330182</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1607282; 1727835</t>
+          <t>1611161; 1727789</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1698387; 1824187</t>
+          <t>1697844; 1820096</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1445705; 1873457</t>
+          <t>1418108; 1510341</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1217806; 1326804</t>
+          <t>1214792; 1330182</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1607282; 1727835</t>
+          <t>1611161; 1727789</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1698387; 1824187</t>
+          <t>1697844; 1820096</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1445705; 1873457</t>
+          <t>1418108; 1510341</t>
         </is>
       </c>
     </row>
